--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T01:53:39+00:00</t>
+    <t>2025-02-14T17:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T17:28:37+00:00</t>
+    <t>2025-02-15T09:32:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-15T09:32:58+00:00</t>
+    <t>2025-02-15T10:51:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-15T10:51:46+00:00</t>
+    <t>2025-02-15T11:51:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-15T11:51:45+00:00</t>
+    <t>2025-02-16T09:15:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-16T09:15:03+00:00</t>
+    <t>2025-02-16T10:07:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-16T10:07:00+00:00</t>
+    <t>2025-02-16T14:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-16T14:15:12+00:00</t>
+    <t>2025-02-16T14:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-16T14:40:01+00:00</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>次回摂取予定日</t>
+    <t>次回接種予定日</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -257,9 +257,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>次回接種予定日</t>
   </si>
   <si>
     <t>次回接種を予定している日、期限</t>
@@ -666,42 +663,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.59765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="10.04296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,10 +845,10 @@
         <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -911,10 +908,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -922,10 +919,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -936,25 +933,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1005,13 +1002,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1020,15 +1017,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1051,13 +1048,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1096,19 +1093,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1120,7 +1117,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1128,10 +1125,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1139,10 +1136,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1154,16 +1151,16 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1213,13 +1210,13 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1228,15 +1225,15 @@
         <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1247,7 +1244,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1259,13 +1256,13 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1316,22 +1313,22 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
